--- a/data/lots/narjiss-lots-jawhara-modele.xlsx
+++ b/data/lots/narjiss-lots-jawhara-modele.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Listes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lots'!$A$1:$T$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lots'!$A$1:$W$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1309,6 +1309,8 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1407,7 +1409,22 @@
           <t>plan_fichier</t>
         </is>
       </c>
-      <c r="T1" s="18" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>plan_architecte</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>plan_visuel</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>visite_360</t>
+        </is>
+      </c>
+      <c r="W1" s="18" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1489,7 +1506,7 @@
       </c>
       <c r="R2" s="20" t="inlineStr"/>
       <c r="S2" s="26" t="inlineStr"/>
-      <c r="T2" s="26" t="inlineStr">
+      <c r="W2" s="26" t="inlineStr">
         <is>
           <t>Local d'angle avec vitrine sur la voie principale</t>
         </is>
@@ -1571,7 +1588,7 @@
       </c>
       <c r="R3" s="20" t="inlineStr"/>
       <c r="S3" s="26" t="inlineStr"/>
-      <c r="T3" s="26" t="inlineStr"/>
+      <c r="W3" s="26" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -1653,7 +1670,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T4" s="26" t="inlineStr"/>
+      <c r="W4" s="26" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -1735,7 +1752,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T5" s="26" t="inlineStr"/>
+      <c r="W5" s="26" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -1817,7 +1834,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T6" s="26" t="inlineStr"/>
+      <c r="W6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -1903,7 +1920,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T7" s="26" t="inlineStr"/>
+      <c r="W7" s="26" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
@@ -1985,7 +2002,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T8" s="26" t="inlineStr"/>
+      <c r="W8" s="26" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -2067,7 +2084,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T9" s="26" t="inlineStr"/>
+      <c r="W9" s="26" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
@@ -2149,7 +2166,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T10" s="26" t="inlineStr"/>
+      <c r="W10" s="26" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
@@ -2231,7 +2248,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T11" s="26" t="inlineStr"/>
+      <c r="W11" s="26" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
@@ -2313,7 +2330,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T12" s="26" t="inlineStr"/>
+      <c r="W12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -2395,7 +2412,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T13" s="26" t="inlineStr">
+      <c r="W13" s="26" t="inlineStr">
         <is>
           <t>Vue degagee sur le jardin interieur</t>
         </is>
@@ -2481,7 +2498,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T14" s="26" t="inlineStr"/>
+      <c r="W14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -2567,7 +2584,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T15" s="26" t="inlineStr"/>
+      <c r="W15" s="26" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
@@ -2649,7 +2666,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T16" s="26" t="inlineStr"/>
+      <c r="W16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
@@ -2731,7 +2748,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T17" s="26" t="inlineStr"/>
+      <c r="W17" s="26" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
@@ -2813,7 +2830,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T18" s="26" t="inlineStr">
+      <c r="W18" s="26" t="inlineStr">
         <is>
           <t>Terrasse privative 22 m2 incluse</t>
         </is>
@@ -2899,7 +2916,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T19" s="26" t="inlineStr"/>
+      <c r="W19" s="26" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
@@ -2981,7 +2998,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T20" s="26" t="inlineStr"/>
+      <c r="W20" s="26" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
@@ -3063,7 +3080,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T21" s="26" t="inlineStr">
+      <c r="W21" s="26" t="inlineStr">
         <is>
           <t>Bloque : reserve au promoteur (logement temoin)</t>
         </is>
@@ -3145,7 +3162,7 @@
       </c>
       <c r="R22" s="20" t="inlineStr"/>
       <c r="S22" s="26" t="inlineStr"/>
-      <c r="T22" s="26" t="inlineStr"/>
+      <c r="W22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
@@ -3223,7 +3240,7 @@
       </c>
       <c r="R23" s="20" t="inlineStr"/>
       <c r="S23" s="26" t="inlineStr"/>
-      <c r="T23" s="26" t="inlineStr"/>
+      <c r="W23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
@@ -3305,7 +3322,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T24" s="26" t="inlineStr">
+      <c r="W24" s="26" t="inlineStr">
         <is>
           <t>Acces direct jardin, ideal famille</t>
         </is>
@@ -3391,7 +3408,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T25" s="26" t="inlineStr"/>
+      <c r="W25" s="26" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
@@ -3473,7 +3490,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T26" s="26" t="inlineStr"/>
+      <c r="W26" s="26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
@@ -3555,7 +3572,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T27" s="26" t="inlineStr"/>
+      <c r="W27" s="26" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
@@ -3637,7 +3654,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T28" s="26" t="inlineStr"/>
+      <c r="W28" s="26" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
@@ -3719,7 +3736,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T29" s="26" t="inlineStr"/>
+      <c r="W29" s="26" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -3801,7 +3818,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T30" s="26" t="inlineStr"/>
+      <c r="W30" s="26" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
@@ -3887,7 +3904,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T31" s="26" t="inlineStr"/>
+      <c r="W31" s="26" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
@@ -3969,7 +3986,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T32" s="26" t="inlineStr"/>
+      <c r="W32" s="26" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
@@ -4051,7 +4068,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T33" s="26" t="inlineStr"/>
+      <c r="W33" s="26" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
@@ -4133,7 +4150,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T34" s="26" t="inlineStr"/>
+      <c r="W34" s="26" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
@@ -4215,7 +4232,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T35" s="26" t="inlineStr"/>
+      <c r="W35" s="26" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
@@ -4297,7 +4314,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T36" s="26" t="inlineStr"/>
+      <c r="W36" s="26" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
@@ -4379,7 +4396,7 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T37" s="26" t="inlineStr"/>
+      <c r="W37" s="26" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
@@ -4461,7 +4478,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T38" s="26" t="inlineStr">
+      <c r="W38" s="26" t="inlineStr">
         <is>
           <t>Terrasse privative 20 m2 incluse</t>
         </is>
@@ -4547,7 +4564,7 @@
           <t>images/projects/jawhara/plans/f2.png</t>
         </is>
       </c>
-      <c r="T39" s="26" t="inlineStr"/>
+      <c r="W39" s="26" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
@@ -4629,7 +4646,7 @@
           <t>images/projects/jawhara/plans/f3.png</t>
         </is>
       </c>
-      <c r="T40" s="26" t="inlineStr"/>
+      <c r="W40" s="26" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
@@ -4711,10 +4728,10 @@
           <t>images/projects/jawhara/plans/f4.png</t>
         </is>
       </c>
-      <c r="T41" s="26" t="inlineStr"/>
+      <c r="W41" s="26" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T41"/>
+  <autoFilter ref="A1:W41"/>
   <dataValidations count="8">
     <dataValidation sqref="E2:E440" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Saisie invalide" error="Valeur non autorisee. Choisir dans la liste deroulante." type="list">
       <formula1>"Studio,F2,F3,F4,F5,Duplex,Bureau,Commerce"</formula1>

--- a/data/lots/narjiss-lots-jawhara-modele.xlsx
+++ b/data/lots/narjiss-lots-jawhara-modele.xlsx
@@ -233,6 +233,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F6F55"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00E4F1EA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009E6300"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FBEEDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001C5FA8"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00E3EDF9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="005A6272"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00ECEEF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B02A2A"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00F7DEDE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4732,6 +4789,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W41"/>
+  <conditionalFormatting sqref="Q2:Q1000">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="0" text="Disponible">
+      <formula>NOT(ISERROR(SEARCH("Disponible",Q2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="0" text="Optionne">
+      <formula>NOT(ISERROR(SEARCH("Optionne",Q2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="0" text="Reserve">
+      <formula>NOT(ISERROR(SEARCH("Reserve",Q2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="3" stopIfTrue="0" text="Vendu">
+      <formula>NOT(ISERROR(SEARCH("Vendu",Q2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="4" stopIfTrue="0" text="Bloque">
+      <formula>NOT(ISERROR(SEARCH("Bloque",Q2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation sqref="E2:E440" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Saisie invalide" error="Valeur non autorisee. Choisir dans la liste deroulante." type="list">
       <formula1>"Studio,F2,F3,F4,F5,Duplex,Bureau,Commerce"</formula1>
